--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:03+00:00</t>
+    <t>2023-03-24T14:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:14+00:00</t>
+    <t>2023-03-24T14:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:14:45+00:00</t>
+    <t>2023-03-24T14:36:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:11+00:00</t>
+    <t>2023-03-24T14:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:59+00:00</t>
+    <t>2023-03-24T14:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:42:38+00:00</t>
+    <t>2023-03-24T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:20+00:00</t>
+    <t>2023-03-24T15:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:53+00:00</t>
+    <t>2023-03-24T15:38:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:38:14+00:00</t>
+    <t>2023-03-26T08:37:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T08:37:00+00:00</t>
+    <t>2023-03-26T08:42:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T08:42:47+00:00</t>
+    <t>2023-03-26T09:01:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:01:05+00:00</t>
+    <t>2023-03-26T09:02:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:02:01+00:00</t>
+    <t>2023-03-26T09:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:07:12+00:00</t>
+    <t>2023-03-26T10:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:39+00:00</t>
+    <t>2023-03-26T10:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:51+00:00</t>
+    <t>2023-03-26T10:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:42:59+00:00</t>
+    <t>2023-03-26T11:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:08:41+00:00</t>
+    <t>2023-03-26T11:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:16:53+00:00</t>
+    <t>2023-03-26T11:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:17:47+00:00</t>
+    <t>2023-03-26T11:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:23:31+00:00</t>
+    <t>2023-03-27T11:26:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T11:26:57+00:00</t>
+    <t>2023-03-27T11:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T11:35:12+00:00</t>
+    <t>2023-03-27T12:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>87</v>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:01:10+00:00</t>
+    <t>2023-03-27T12:02:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:02:15+00:00</t>
+    <t>2023-03-27T12:10:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:10:50+00:00</t>
+    <t>2023-03-28T07:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:37:59+00:00</t>
+    <t>2023-03-28T07:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:45:58+00:00</t>
+    <t>2023-03-28T07:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:53:05+00:00</t>
+    <t>2023-03-29T10:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:46:03+00:00</t>
+    <t>2023-03-29T10:52:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:52:43+00:00</t>
+    <t>2023-03-29T11:10:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T11:10:06+00:00</t>
+    <t>2023-03-31T13:54:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:54:07+00:00</t>
+    <t>2023-03-31T13:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:55:03+00:00</t>
+    <t>2023-04-01T08:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:28:06+00:00</t>
+    <t>2023-04-01T08:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:29:12+00:00</t>
+    <t>2023-04-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:49:37+00:00</t>
+    <t>2023-04-01T08:50:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:50:39+00:00</t>
+    <t>2023-04-03T05:56:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T05:56:04+00:00</t>
+    <t>2023-04-03T09:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:35:38+00:00</t>
+    <t>2023-04-03T09:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:37:11+00:00</t>
+    <t>2023-04-03T09:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:57:00+00:00</t>
+    <t>2023-04-03T10:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:19:29+00:00</t>
+    <t>2023-04-03T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:20:09+00:00</t>
+    <t>2023-04-03T10:41:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:41:47+00:00</t>
+    <t>2023-04-04T06:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:46:45+00:00</t>
+    <t>2023-04-04T06:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:47:21+00:00</t>
+    <t>2023-04-04T07:17:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T07:17:27+00:00</t>
+    <t>2023-04-04T08:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:23:07+00:00</t>
+    <t>2023-04-04T08:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:37:07+00:00</t>
+    <t>2023-04-04T09:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:08:50+00:00</t>
+    <t>2023-04-04T09:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:09:26+00:00</t>
+    <t>2023-04-04T09:19:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:19:23+00:00</t>
+    <t>2023-04-04T09:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:25:44+00:00</t>
+    <t>2023-04-04T10:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:05:29+00:00</t>
+    <t>2023-04-04T10:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:21:49+00:00</t>
+    <t>2023-04-04T10:30:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:30:43+00:00</t>
+    <t>2023-04-04T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:10+00:00</t>
+    <t>2023-04-04T10:41:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:37+00:00</t>
+    <t>2023-04-04T10:49:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:49:31+00:00</t>
+    <t>2023-04-04T13:12:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:12:12+00:00</t>
+    <t>2023-04-04T13:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:39:29+00:00</t>
+    <t>2023-04-17T11:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:49:04+00:00</t>
+    <t>2023-04-17T12:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:05:39+00:00</t>
+    <t>2023-04-17T12:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2676" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2678" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:49:16+00:00</t>
+    <t>2023-05-26T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -1578,7 +1578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1665,77 +1665,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:19+00:00</t>
+    <t>2023-05-26T12:35:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:50+00:00</t>
+    <t>2023-05-26T12:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:45:45+00:00</t>
+    <t>2023-05-26T12:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:47:23+00:00</t>
+    <t>2023-05-26T13:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:04:11+00:00</t>
+    <t>2023-05-26T13:05:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:05:32+00:00</t>
+    <t>2023-05-26T13:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:09:55+00:00</t>
+    <t>2023-05-26T14:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:47:38+00:00</t>
+    <t>2023-05-26T14:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:52:17+00:00</t>
+    <t>2023-05-26T14:59:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:59:52+00:00</t>
+    <t>2023-05-26T15:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:03:26+00:00</t>
+    <t>2023-05-26T15:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:10:57+00:00</t>
+    <t>2023-05-29T05:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-29T05:00:29+00:00</t>
+    <t>2023-05-29T05:09:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-12T13:14:32+00:00</t>
+    <t>2023-06-13T16:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:44:52+00:00</t>
+    <t>2023-06-13T16:48:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:48:27+00:00</t>
+    <t>2023-06-13T16:56:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:56:41+00:00</t>
+    <t>2023-06-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-20T13:48:39+00:00</t>
+    <t>2023-06-20T13:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-transferring-facility-encounter.xlsx
+++ b/StructureDefinition-transferring-facility-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-20T13:48:52+00:00</t>
+    <t>2023-06-20T13:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
